--- a/ch_08_simulations_scenarios/ch_08_solution.xlsx
+++ b/ch_08_simulations_scenarios/ch_08_solution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\python-in-excel-book-staging\new_datasets\ch_08_simulations_scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_08_simulations_scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDC5F1C-7886-4E40-B48F-3E2E47FFC84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6763623-1E7A-4150-90D7-386467A0D74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -72,27 +72,13 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="3">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -101,12 +87,6 @@
     </bk>
     <bk>
       <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -160,14 +140,19 @@
     </pythonScript>
     <pythonScript>
       <code># Set random seed for reproducibility
-np.random.seed(1234)
+np.random.seed(42)
+# Number of simulations
 num_simulations = 10000
 # Business parameters
 selling_price = 50
 cost_per_unit = 30
 inventory_available = 1100
-# Generate random demand (normal distribution, cannot be negative)
-demand = np.maximum(np.random.normal(1000, 200, num_simulations), 0)
+# Generate random demand (normal distribution, non-negative)
+demand = np.maximum(
+    np.random.normal(1000, 200, num_simulations),
+    0
+)
+# Preview first 5 values
 demand[:5]</code>
     </pythonScript>
     <pythonScript>
@@ -182,19 +167,28 @@
 profit[:5]</code>
     </pythonScript>
     <pythonScript>
-      <code>mean_profit = np.mean(profit)
-median_profit = np.median(profit)
-percentile_10 = np.percentile(profit, 10)
-percentile_90 = np.percentile(profit, 90)
-prob_loss = (profit &lt; 0).sum() / num_simulations
+      <code># Summary statistics
+mean_profit      = np.mean(profit)
+median_profit    = np.median(profit)
+percentile_10    = np.percentile(profit, 10)
+percentile_90    = np.percentile(profit, 90)
+prob_loss        = (profit &lt; 0).sum() / num_simulations
+# Store results in a DataFrame (no formatting applied)
 results = pd.DataFrame({
-    "Metric": ["Mean Profit", "Median Profit", "10th Percentile",
-               "90th Percentile", "Probability of Loss"],
-    "Value": ["$" + str(round(mean_profit)),
-              "$" + str(round(median_profit)),
-              "$" + str(round(percentile_10)),
-              "$" + str(round(percentile_90)),
-              str(round(prob_loss * 100, 2)) + "%%"]
+    "Metric": [
+        "Mean Profit",
+        "Median Profit",
+        "10th Percentile",
+        "90th Percentile",
+        "Probability of Loss"
+    ],
+    "Value": [
+        mean_profit,
+        median_profit,
+        percentile_10,
+        percentile_90,
+        prob_loss
+    ]
 })
 results</code>
     </pythonScript>
@@ -210,14 +204,20 @@
 plt.legend()</code>
     </pythonScript>
     <pythonScript>
-      <code>prob_high_profit = (profit &gt; 18000).sum() / num_simulations
-"Probability of profit &gt; $18,000: " + str(round(prob_high_profit * 100, 1)) + "%%"</code>
+      <code># Probability of high profit
+prob_high_profit = (profit &gt; 18000).sum() / num_simulations
+# Display result
+f"Probability of profit &gt; $18,000: {prob_high_profit * 100:.1f}%%"</code>
     </pythonScript>
     <pythonScript>
-      <code>np.random.seed(42)
-# Same demand for all three decisions
-demand = np.maximum(np.random.normal(1000, 200, num_simulations), 0)
-# Test three inventory levels
+      <code># Set random seed for reproducibility
+np.random.seed(42)
+# Generate demand (same across scenarios)
+demand = np.maximum(
+    np.random.normal(1000, 200, num_simulations),
+    0
+)
+# Inventory options to test
 inventory_options = [900, 1100, 1300]
 results_list = []
 for inv in inventory_options:
@@ -231,8 +231,9 @@
         "Median Profit": round(np.median(sim_profit)),
         "10th Pctile": round(np.percentile(sim_profit, 10)),
         "90th Pctile": round(np.percentile(sim_profit, 90)),
-        "Prob of Loss": str(round((sim_profit &lt; 0).sum() / num_simulations * 100, 1)) + "%%"
+        "Prob of Loss": (sim_profit &lt; 0).sum() / num_simulations
     })
+# Create comparison table
 comparison = pd.DataFrame(results_list)
 comparison</code>
     </pythonScript>
@@ -258,6 +259,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -287,8 +292,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -317,7 +326,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>503767</xdr:colOff>
+      <xdr:colOff>601134</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>134298</xdr:rowOff>
     </xdr:to>
@@ -366,7 +375,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>514576</xdr:colOff>
+      <xdr:colOff>235176</xdr:colOff>
       <xdr:row>53</xdr:row>
       <xdr:rowOff>155803</xdr:rowOff>
     </xdr:to>
@@ -415,7 +424,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>197502</xdr:colOff>
+      <xdr:colOff>294869</xdr:colOff>
       <xdr:row>79</xdr:row>
       <xdr:rowOff>59267</xdr:rowOff>
     </xdr:to>
@@ -499,34 +508,18 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <rv s="0">
-    <fb t="s">Mean heads per 100 flips: 49.98, Std dev: 5.01</fb>
-    <v>&lt;class 'str'&gt;</v>
-    <v>str</v>
-    <v>Mean heads per 100 flips: 49.98, Std dev: 5.01</v>
-    <v>Mean heads per 100 flips: 49.98, Std dev: 5.01</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
     <v>0</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="1">
+  <rv s="0">
     <v>1</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
   <rv s="0">
-    <fb t="s">Probability of profit &gt; $18,000: 46.6%</fb>
-    <v>&lt;class 'str'&gt;</v>
-    <v>str</v>
-    <v>Probability of profit &gt; $18,000: 46.6%</v>
-    <v>Probability of profit &gt; $18,000: 46.6%</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
     <v>2</v>
     <v>9</v>
     <v>Image generated by Python</v>
@@ -535,42 +528,13 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
-  <s t="_python">
-    <k n="Python_type" t="s"/>
-    <k n="Python_typeName" t="s"/>
-    <k n="Python_str" t="s"/>
-    <k n="basicValue" t="s"/>
-    <k n="_Provider" t="spb"/>
-  </s>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
   <s t="_localImage">
     <k n="_rvRel:LocalImageIdentifier" t="i"/>
     <k n="CalcOrigin" t="i"/>
     <k n="Text" t="s"/>
   </s>
 </rvStructures>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
-<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="1">
-    <spb s="0">
-      <v>https://www.anaconda.com/excel</v>
-      <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
-      <v>Python provided by Anaconda</v>
-    </spb>
-  </spbData>
-</supportingPropertyBags>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
-  <s>
-    <k n="link" t="s"/>
-    <k n="logo" t="s"/>
-    <k n="name" t="s"/>
-  </s>
-</spbStructures>
 </file>
 
 <file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
@@ -847,7 +811,10 @@
   <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="19.64453125" customWidth="1"/>
+    <col min="1" max="1" width="14.41015625" customWidth="1"/>
+    <col min="2" max="2" width="9.703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5859375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.17578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.5">
@@ -877,68 +844,77 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A8" t="str" cm="1" vm="1">
-        <f t="array" ref="A8">_xlfn._xlws.PY(1,1)</f>
+      <c r="A8" t="str" cm="1">
+        <f t="array" ref="A8">_xlfn._xlws.PY(1,0)</f>
         <v>Mean heads per 100 flips: 49.98, Std dev: 5.01</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A11" t="e" cm="1" vm="2">
+      <c r="A11" t="e" cm="1" vm="1">
         <f t="array" ref="A11">_xlfn._xlws.PY(2,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A23" cm="1">
+      <c r="A23" s="1" cm="1">
         <f t="array" ref="A23:A27">_xlfn._xlws.PY(3,0)</f>
-        <v>1094.2870327464987</v>
+        <v>1099.3428306022465</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A24">
-        <v>761.80486105870705</v>
+      <c r="A24" s="1">
+        <v>972.34713976576302</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A25">
-        <v>1286.5413936852194</v>
+      <c r="A25" s="1">
+        <v>1129.5377076201385</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A26">
-        <v>937.46962078165745</v>
+      <c r="A26" s="1">
+        <v>1304.605971281605</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A27">
-        <v>855.88225332699767</v>
-      </c>
+      <c r="A27" s="1">
+        <v>953.16932505533282</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A29" s="1"/>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A30" cm="1">
+      <c r="A30" s="1" cm="1">
         <f t="array" ref="A30:A34">_xlfn._xlws.PY(4,0)</f>
-        <v>21714.351637324929</v>
+        <v>21967.141530112327</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A31">
-        <v>5090.2430529353514</v>
+      <c r="A31" s="1">
+        <v>15617.356988288149</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A32">
+      <c r="A32" s="1">
         <v>22000</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A33">
-        <v>13873.481039082872</v>
+      <c r="A33" s="1">
+        <v>22000</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A34">
-        <v>9794.1126663498871</v>
-      </c>
+      <c r="A34" s="1">
+        <v>14658.466252766644</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A35" s="1"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A36" t="str" cm="1">
@@ -953,52 +929,52 @@
       <c r="A37" t="str">
         <v>Mean Profit</v>
       </c>
-      <c r="B37" t="str">
-        <v>$15152</v>
+      <c r="B37" s="1">
+        <v>14998.252053092408</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A38" t="str">
         <v>Median Profit</v>
       </c>
-      <c r="B38" t="str">
-        <v>$17181</v>
+      <c r="B38" s="1">
+        <v>16974.050242071222</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A39" t="str">
         <v>10th Percentile</v>
       </c>
-      <c r="B39" t="str">
-        <v>$4191</v>
+      <c r="B39" s="1">
+        <v>4077.0103968971662</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A40" t="str">
         <v>90th Percentile</v>
       </c>
-      <c r="B40" t="str">
-        <v>$22000</v>
+      <c r="B40" s="1">
+        <v>22000</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A41" t="str">
         <v>Probability of Loss</v>
       </c>
-      <c r="B41" t="str">
-        <v>4.55%</v>
+      <c r="B41" s="2">
+        <v>4.65E-2</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A44" t="e" cm="1" vm="3">
+      <c r="A44" t="e" cm="1" vm="2">
         <f t="array" ref="A44">_xlfn._xlws.PY(6,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A58" t="str" cm="1" vm="4">
-        <f t="array" ref="A58">_xlfn._xlws.PY(7,1)</f>
-        <v>Probability of profit &gt; $18,000: 46.6%</v>
+      <c r="A58" t="str" cm="1">
+        <f t="array" ref="A58">_xlfn._xlws.PY(7,0)</f>
+        <v>Probability of profit &gt; $18,000: 45.9%</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.5">
@@ -1018,72 +994,72 @@
       <c r="E62" t="str">
         <v>90th Pctile</v>
       </c>
-      <c r="F62" t="str">
+      <c r="F62" s="2" t="str">
         <v>Prob of Loss</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A63">
+      <c r="A63" s="3">
         <v>900</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="4">
         <v>16007</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="4">
         <v>18000</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="4">
         <v>10077</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="4">
         <v>18000</v>
       </c>
-      <c r="F63" t="str">
-        <v>1.1%</v>
+      <c r="F63" s="2">
+        <v>1.06E-2</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A64">
+      <c r="A64" s="3">
         <v>1100</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="4">
         <v>14998</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="4">
         <v>16974</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="4">
         <v>4077</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="4">
         <v>22000</v>
       </c>
-      <c r="F64" t="str">
-        <v>4.6%</v>
+      <c r="F64" s="2">
+        <v>4.65E-2</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A65">
+      <c r="A65" s="3">
         <v>1300</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="4">
         <v>10681</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="4">
         <v>10974</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="4">
         <v>-1923</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="4">
         <v>23813</v>
       </c>
-      <c r="F65" t="str">
-        <v>13.5%</v>
+      <c r="F65" s="2">
+        <v>0.13539999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A68" t="e" cm="1" vm="5">
+      <c r="A68" t="e" cm="1" vm="3">
         <f t="array" ref="A68">_xlfn._xlws.PY(9,0)</f>
         <v>#VALUE!</v>
       </c>
